--- a/output/excel/bnl_10K_2024_classified.xlsx
+++ b/output/excel/bnl_10K_2024_classified.xlsx
@@ -531,306 +531,306 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Accounted for using the direct financing method</t>
+          <t xml:space="preserve">      Land</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>26,154</t>
+          <t>$ 778,826</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>26,643</t>
+          <t>$ 748,529</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Accounted for using the sales-type method</t>
+          <t xml:space="preserve">      Land improvements</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>357,142</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>328,746</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Property under development</t>
+          <t xml:space="preserve">      Buildings and improvements</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>18,784</t>
+          <t>3,815,521</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>94,964</t>
+          <t>3,803,156</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Investment in rental property, net</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>4,340,363</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>4,384,278</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Equipment</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>15,843</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>8,265</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>14,845</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>19,494</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total accounted for using the operating method</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>4,967,332</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>4,888,696</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Accrued rental income</t>
+          <t xml:space="preserve">      Less accumulated depreciation</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>162,717</t>
+          <t>(672,478)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>152,724</t>
+          <t>(626,597)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tenant and other receivables, net</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>3,281</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1,487</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Accounted for using the operating method, net</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>4,294,854</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>4,262,099</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Prepaid expenses and other assets</t>
+          <t xml:space="preserve">   Accounted for using the direct financing method</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>41,584</t>
+          <t>26,154</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>36,661</t>
+          <t>26,643</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Interest rate swap, assets</t>
+          <t xml:space="preserve">   Accounted for using the sales-type method</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>46,220</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>46,096</t>
+          <t>572</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Goodwill</t>
+          <t xml:space="preserve">   Property under development</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>339,769</t>
+          <t>18,784</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>339,769</t>
+          <t>94,964</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Intangible lease assets, net</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>267,638</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>288,226</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Investment in rental property, net</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>4,340,363</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>4,384,278</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Land</t>
+          <t xml:space="preserve">   Cash and cash equivalents</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>$ 778,826</t>
+          <t>14,845</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$ 748,529</t>
+          <t>19,494</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Land improvements</t>
+          <t xml:space="preserve">   Accrued rental income</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>357,142</t>
+          <t>162,717</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>328,746</t>
+          <t>152,724</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Buildings and improvements</t>
+          <t xml:space="preserve">   Tenant and other receivables, net</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>3,815,521</t>
+          <t>3,281</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>3,803,156</t>
+          <t>1,487</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Equipment</t>
+          <t xml:space="preserve">   Prepaid expenses and other assets</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>15,843</t>
+          <t>41,584</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>8,265</t>
+          <t>36,661</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total accounted for using the operating method</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>4,967,332</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>4,888,696</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Interest rate swap, assets</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>46,220</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>46,096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Less accumulated depreciation</t>
+          <t xml:space="preserve">   Goodwill</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>(672,478)</t>
+          <t>339,769</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>(626,597)</t>
+          <t>339,769</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Accounted for using the operating method, net</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>4,294,854</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>4,262,099</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Intangible lease assets, net</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>267,638</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>288,226</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t xml:space="preserve">   Total liabilities</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Commitments and contingencies (Note 17)</t>
+          <t xml:space="preserve">   Commitments and contingencies (Note 17)</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr"/>
@@ -1043,119 +1043,119 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Non-controlling interests</t>
+          <t xml:space="preserve">      Preferred stock, $0.001 par value; 20,000 shares authorized, no shares issued or outstanding</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>137,679</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>145,100</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Preferred stock, $0.001 par value; 20,000 shares authorized, no shares issued or outstanding</t>
+          <t xml:space="preserve">      Common stock, $0.00025 par value; 500,000 shares authorized, 188,626 and 187,614 shares issued and outstanding at December 31, 2024 and 2023, respectively</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Common stock, $0.00025 par value; 500,000 shares authorized, 188,626 and 187,614 shares issued and outstanding at December 31, 2024 and 2023, respectively</t>
+          <t xml:space="preserve">      Additional paid-in capital</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>3,450,584</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>3,440,639</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Additional paid-in capital</t>
+          <t xml:space="preserve">      Cumulative distributions in excess of retained earnings</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>3,450,584</t>
+          <t>(496,543)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>3,440,639</t>
+          <t>(440,731)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Cumulative distributions in excess of retained earnings</t>
+          <t xml:space="preserve">      Accumulated other comprehensive income</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>(496,543)</t>
+          <t>49,657</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>(440,731)</t>
+          <t>49,286</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accumulated other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>49,657</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>49,286</t>
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total Broadstone Net Lease, Inc. equity</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>3,003,745</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>3,049,241</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total Broadstone Net Lease, Inc. equity</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>3,003,745</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>3,049,241</t>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>137,679</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>145,100</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Lease revenues, net</t>
+          <t xml:space="preserve">   Lease revenues, net</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
+          <t xml:space="preserve">   Depreciation and amortization</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Property and operating expense</t>
+          <t xml:space="preserve">   Property and operating expense</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t xml:space="preserve">   General and administrative</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Provision for impairment of investment in rental properties</t>
+          <t xml:space="preserve">   Provision for impairment of investment in rental properties</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1386,7 +1386,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t xml:space="preserve">   Total operating expenses</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t xml:space="preserve">   Interest income</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t xml:space="preserve">   Interest expense</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Gain on sale of real estate</t>
+          <t xml:space="preserve">   Gain on sale of real estate</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1484,7 +1484,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t xml:space="preserve">   Income taxes</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t xml:space="preserve">   Other income (expenses)</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1528,7 +1528,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t xml:space="preserve">   Net income</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Net income attributable to non-controlling interests</t>
+          <t xml:space="preserve">   Net income attributable to non-controlling interests</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1570,22 +1570,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Net income attributable to Broadstone Net Lease, Inc.</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income attributable to Broadstone Net Lease, Inc.</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>$ 162,441</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>$ 155,478</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>$ 122,115</t>
         </is>
@@ -1604,7 +1604,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t xml:space="preserve">   Basic</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1626,7 +1626,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t xml:space="preserve">   Diluted</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Basic and Diluted</t>
+          <t xml:space="preserve">   Basic and Diluted</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t xml:space="preserve">   Net income</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1710,122 +1710,122 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr"/>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="6" t="inlineStr"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Comprehensive income</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>169,322</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>147,902</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>222,549</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Change in fair value of interest rate swaps</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>(17,293)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>90,560</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Comprehensive income attributable to non-controlling interests</t>
+          <t xml:space="preserve">   Realized loss on interest rate swaps</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>(6,552)</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>(7,070)</t>
+          <t>1,883</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>(12,700)</t>
+          <t>2,514</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Comprehensive income attributable to Broadstone Net Lease, Inc.</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>$ 162,770</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>$ 140,832</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>$ 209,849</t>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Comprehensive income</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>169,322</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>147,902</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>222,549</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Change in fair value of interest rate swaps</t>
+          <t xml:space="preserve">   Comprehensive income attributable to non-controlling interests</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>(6,552)</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>(17,293)</t>
+          <t>(7,070)</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>90,560</t>
+          <t>(12,700)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Realized loss on interest rate swaps</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>1,883</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>2,514</t>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Comprehensive income attributable to Broadstone Net Lease, Inc.</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>$ 162,770</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>$ 140,832</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>$ 209,849</t>
         </is>
       </c>
     </row>
@@ -1901,37 +1901,37 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Balance, January 1, 2022</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance, January 1, 2022</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;41</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;2,924,168</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;(318,476)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;(28,441)</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;163,846</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;2,741,138</t>
         </is>
@@ -1940,7 +1940,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t xml:space="preserve">   Net income</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1977,7 +1977,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Issuance of 23,682 shares of common stock</t>
+          <t xml:space="preserve">   Issuance of 23,682 shares of common stock</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Offering costs, discounts, and commissions</t>
+          <t xml:space="preserve">   Offering costs, discounts, and commissions</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Stock-based compensation, net of ten shares of restricted stock forfeited</t>
+          <t xml:space="preserve">   Stock-based compensation, net of ten shares of restricted stock forfeited</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Retirement of 59 shares of common stock under equity incentive plan</t>
+          <t xml:space="preserve">   Retirement of 59 shares of common stock under equity incentive plan</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Conversion of 118 OP Units to 118 shares of common stock</t>
+          <t xml:space="preserve">   Conversion of 118 OP Units to 118 shares of common stock</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2162,7 +2162,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Distributions declared ($1.080 per share and OP Unit)</t>
+          <t xml:space="preserve">   Distributions declared ($1.080 per share and OP Unit)</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2199,7 +2199,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Change in fair value of interest rate swap agreements</t>
+          <t xml:space="preserve">   Change in fair value of interest rate swap agreements</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Realized loss on interest rate swap agreements</t>
+          <t xml:space="preserve">   Realized loss on interest rate swap agreements</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Adjustment to non-controlling interests</t>
+          <t xml:space="preserve">   Adjustment to non-controlling interests</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -2308,37 +2308,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2022</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance, December 31, 2022</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>3,419,395</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>(386,049)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>59,525</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>169,587</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>3,262,505</t>
         </is>
@@ -2347,7 +2347,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t xml:space="preserve">   Net income</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Issuance of 312 shares of common stock under equity incentive plan</t>
+          <t xml:space="preserve">   Issuance of 312 shares of common stock under equity incentive plan</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Offering costs, discounts, and commissions</t>
+          <t xml:space="preserve">   Offering costs, discounts, and commissions</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Stock-based compensation, net of 23 shares of restricted stock forfeited</t>
+          <t xml:space="preserve">   Stock-based compensation, net of 23 shares of restricted stock forfeited</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Retirement of 66 shares of common stock under equity incentive plan</t>
+          <t xml:space="preserve">   Retirement of 66 shares of common stock under equity incentive plan</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Conversion of 1,277 OP Units to 1,277 shares of common stock</t>
+          <t xml:space="preserve">   Conversion of 1,277 OP Units to 1,277 shares of common stock</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Distributions declared ($1.120 per share and OP Unit)</t>
+          <t xml:space="preserve">   Distributions declared ($1.120 per share and OP Unit)</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Change in fair value of interest rate swap agreements</t>
+          <t xml:space="preserve">   Change in fair value of interest rate swap agreements</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Realized loss on interest rate swap agreements</t>
+          <t xml:space="preserve">   Realized loss on interest rate swap agreements</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2680,7 +2680,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Adjustment to non-controlling interests</t>
+          <t xml:space="preserve">   Adjustment to non-controlling interests</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2715,37 +2715,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2023</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance, December 31, 2023</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>3,440,639</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>(440,731)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>49,286</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>145,100</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>3,194,341</t>
         </is>
@@ -2754,7 +2754,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t xml:space="preserve">   Net income</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Issuance of 893 shares of common stock under equity incentive plan</t>
+          <t xml:space="preserve">   Issuance of 893 shares of common stock under equity incentive plan</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2828,7 +2828,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Offering costs, discounts, and commissions</t>
+          <t xml:space="preserve">   Offering costs, discounts, and commissions</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Contributions from non-controlling interests</t>
+          <t xml:space="preserve">   Contributions from non-controlling interests</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Stock-based compensation, net of 92 shares of restricted stock forfeited</t>
+          <t xml:space="preserve">   Stock-based compensation, net of 92 shares of restricted stock forfeited</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Retirement of 71 shares of common stock under equity incentive plan</t>
+          <t xml:space="preserve">   Retirement of 71 shares of common stock under equity incentive plan</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2972,7 +2972,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Conversion of 282 OP Units to 282 shares of common stock</t>
+          <t xml:space="preserve">   Conversion of 282 OP Units to 282 shares of common stock</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Distributions declared ($1.155 per share and OP Unit)</t>
+          <t xml:space="preserve">   Distributions declared ($1.155 per share and OP Unit)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Change in fair value of interest rate swap agreements</t>
+          <t xml:space="preserve">   Change in fair value of interest rate swap agreements</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Realized loss on interest rate swap agreements</t>
+          <t xml:space="preserve">   Realized loss on interest rate swap agreements</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -3120,7 +3120,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Adjustment to non-controlling interests</t>
+          <t xml:space="preserve">   Adjustment to non-controlling interests</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -3155,37 +3155,37 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2024</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance, December 31, 2024</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;47</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;3,450,584</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;(496,543</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;49,657</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;137,679</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>$&lt;br&gt;3,141,424</t>
         </is>
@@ -3285,7 +3285,8 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Adjustments to reconcile net income including non-controlling interests to net cash provided by operating activities:</t>
+          <t xml:space="preserve">   Adjustments to reconcile net income including non-controlling interests to net cash
+provided by operating activities:</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
@@ -3293,276 +3294,277 @@
       <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Changes in assets and liabilities:</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Depreciation and amortization including intangibles associated with
+investment in rental property</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>151,765</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>152,781</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>149,998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Net cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>276,253</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>271,074</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>255,914</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Provision for impairment of investment in rental properties</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>49,001</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>31,274</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>5,535</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Depreciation and amortization including intangibles associated with investment in rental property</t>
+          <t xml:space="preserve">      Amortization of debt issuance costs and original issuance discounts charged to interest expense</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>151,765</t>
+          <t>3,932</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>152,781</t>
+          <t>3,860</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>149,998</t>
+          <t>3,588</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Provision for impairment of investment in rental properties</t>
+          <t xml:space="preserve">      Stock-based compensation expense</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>49,001</t>
+          <t>7,355</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>31,274</t>
+          <t>6,359</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>5,535</t>
+          <t>5,316</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Amortization of debt issuance costs and original issuance discounts charged to interest expense</t>
+          <t xml:space="preserve">      Straight-line rent, direct financing and sales-type lease adjustments</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>3,932</t>
+          <t>(18,975)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>3,860</t>
+          <t>(22,278)</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>3,588</t>
+          <t>(20,494)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Stock-based compensation expense</t>
+          <t xml:space="preserve">      Gain on sale of real estate</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>7,355</t>
+          <t>(73,153)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>6,359</t>
+          <t>(54,310)</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>5,316</t>
+          <t>(15,953)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Straight-line rent, direct financing and sales-type lease adjustments</t>
+          <t xml:space="preserve">      Other non-cash items</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>(18,975)</t>
+          <t>(10,629)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>(22,278)</t>
+          <t>(757)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>(20,494)</t>
+          <t>(1,858)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Gain on sale of real estate</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>(73,153)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>(54,310)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>(15,953)</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Changes in assets and liabilities:</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Other non-cash items</t>
+          <t xml:space="preserve">      Tenant and other receivables</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>(10,629)</t>
+          <t>(1,742)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>(757)</t>
+          <t>780</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>(1,858)</t>
+          <t>659</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Tenant and other receivables</t>
+          <t xml:space="preserve">      Prepaid expenses and other assets</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>(1,742)</t>
+          <t>480</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>(352)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Prepaid expenses and other assets</t>
+          <t xml:space="preserve">      Accounts payable and other liabilities</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>(905)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>(352)</t>
+          <t>(8,226)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>(1,149)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Accounts payable and other liabilities</t>
+          <t xml:space="preserve">      Accrued interest payable</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>(905)</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>(8,226)</t>
+          <t>(1,369)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>(1,149)</t>
+          <t>598</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued interest payable</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>(1,369)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>598</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net cash provided by operating activities</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>276,253</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>271,074</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>255,914</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3723,8 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Proceeds from issuance of common stock, net of $996, $180, and $7,492 of offering costs, discounts, and commissions in 2024, 2023 and 2022, respectively</t>
+          <t xml:space="preserve">   Proceeds from issuance of common stock, net of $996, $180, and $7,492 of offering costs,
+discounts, and commissions in 2024, 2023 and 2022, respectively</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
